--- a/Base/Biochar_Onion_Pea_Final.xlsx
+++ b/Base/Biochar_Onion_Pea_Final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30210"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACB8A775-5CF9-44C0-B19E-B1405383146C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{880DC774-E4CD-42B5-AF0D-B63318110710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="18350" windowHeight="6800" firstSheet="13" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="30">
   <si>
     <t>Control</t>
   </si>
@@ -85,9 +85,6 @@
     <t>R10</t>
   </si>
   <si>
-    <t>Mean</t>
-  </si>
-  <si>
     <t>Day 3</t>
   </si>
   <si>
@@ -101,6 +98,9 @@
   </si>
   <si>
     <t>Biochar Concentration</t>
+  </si>
+  <si>
+    <t>Mean</t>
   </si>
   <si>
     <t>SD</t>
@@ -303,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -328,9 +328,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -406,17 +403,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -706,10 +697,10 @@
                   <c:v>2.37</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.19</c:v>
+                  <c:v>2.1900000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.58</c:v>
+                  <c:v>2.5800000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2.08</c:v>
@@ -855,7 +846,7 @@
                   <c:v>5.54</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.13</c:v>
+                  <c:v>4.1300000000000008</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -992,10 +983,10 @@
                   <c:v>6.36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.39</c:v>
+                  <c:v>7.3899999999999988</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.54</c:v>
+                  <c:v>7.5400000000000009</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.61</c:v>
@@ -1535,7 +1526,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.68</c:v>
+                  <c:v>14.680000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>7.76</c:v>
@@ -2071,7 +2062,7 @@
                   <c:v>15.24</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.08</c:v>
+                  <c:v>15.080000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>15.3</c:v>
@@ -2622,10 +2613,10 @@
                   <c:v>13.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.72</c:v>
+                  <c:v>14.720000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.68</c:v>
+                  <c:v>11.679999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>11.66</c:v>
@@ -3176,7 +3167,7 @@
                   <c:v>22.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31.36</c:v>
+                  <c:v>31.360000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3715,7 +3706,7 @@
                   <c:v>19.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31.36</c:v>
+                  <c:v>31.360000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4254,7 +4245,7 @@
                   <c:v>17.399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31.36</c:v>
+                  <c:v>31.360000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4699,16 +4690,16 @@
                   <c:formatCode>General</c:formatCode>
                   <c:ptCount val="5"/>
                   <c:pt idx="0">
-                    <c:v>2.12</c:v>
+                    <c:v>2.0299999999999998</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>4.12</c:v>
+                    <c:v>4.32</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>2.72</c:v>
+                    <c:v>1.89</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>3.84</c:v>
+                    <c:v>4.03</c:v>
                   </c:pt>
                   <c:pt idx="4">
                     <c:v>0.86</c:v>
@@ -4723,16 +4714,16 @@
                   <c:formatCode>General</c:formatCode>
                   <c:ptCount val="5"/>
                   <c:pt idx="0">
-                    <c:v>2.12</c:v>
+                    <c:v>2.0299999999999998</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>4.12</c:v>
+                    <c:v>4.32</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>2.72</c:v>
+                    <c:v>1.89</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>3.84</c:v>
+                    <c:v>4.03</c:v>
                   </c:pt>
                   <c:pt idx="4">
                     <c:v>0.86</c:v>
@@ -4781,19 +4772,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>35.799999999999997</c:v>
+                  <c:v>35.274999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36.58</c:v>
+                  <c:v>37.35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34.4</c:v>
+                  <c:v>35.375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>26.88</c:v>
+                  <c:v>27.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31.36</c:v>
+                  <c:v>31.360000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5329,7 +5320,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.26</c:v>
+                  <c:v>1.2600000000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.5</c:v>
@@ -5472,19 +5463,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.35</c:v>
+                  <c:v>2.3500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.92</c:v>
+                  <c:v>2.9200000000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.77</c:v>
+                  <c:v>3.7700000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.69</c:v>
+                  <c:v>5.6899999999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.13</c:v>
+                  <c:v>4.1300000000000008</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5615,16 +5606,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3.24</c:v>
+                  <c:v>3.2399999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3.79</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.88</c:v>
+                  <c:v>4.8800000000000008</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.16</c:v>
+                  <c:v>7.1599999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5.61</c:v>
@@ -6309,7 +6300,7 @@
                   <c:v>6.13</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.13</c:v>
+                  <c:v>4.1300000000000008</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7134,7 +7125,7 @@
                   <c:v>4.78</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.13</c:v>
+                  <c:v>4.1300000000000008</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7807,7 +7798,7 @@
                   <c:v>20.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.84</c:v>
+                  <c:v>19.839999999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>14.9</c:v>
@@ -7816,7 +7807,7 @@
                   <c:v>12.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.920000000000002</c:v>
+                  <c:v>16.919999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8008,13 +7999,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Acrostichum shoot '!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Acrostichum shoot '!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:plus>
@@ -8023,13 +8017,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Acrostichum shoot '!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Acrostichum shoot '!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:minus>
@@ -8616,7 +8613,7 @@
                   <c:v>11.44</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.920000000000002</c:v>
+                  <c:v>16.919999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8808,13 +8805,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Quisqualis indica Shoot'!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Quisqualis indica Shoot'!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:plus>
@@ -8823,13 +8823,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Quisqualis indica Shoot'!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Quisqualis indica Shoot'!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:minus>
@@ -9413,7 +9416,7 @@
                   <c:v>7.54</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.920000000000002</c:v>
+                  <c:v>16.919999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9605,13 +9608,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Ludwigia peruviana Shoot'!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Ludwigia peruviana Shoot'!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:plus>
@@ -9620,13 +9626,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Ludwigia peruviana Shoot'!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Ludwigia peruviana Shoot'!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:minus>
@@ -10210,7 +10219,7 @@
                   <c:v>7.76</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.920000000000002</c:v>
+                  <c:v>16.919999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10402,13 +10411,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Cyclosorus interruptus Shoot'!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Cyclosorus interruptus Shoot'!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:plus>
@@ -10417,13 +10429,16 @@
                       <c:extLst>
                         <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                           <c15:formulaRef>
-                            <c15:sqref>'Cyclosorus interruptus Shoot'!$H$12:$H$16</c15:sqref>
+                            <c15:sqref>'Cyclosorus interruptus Shoot'!#REF!</c15:sqref>
                           </c15:formulaRef>
                         </c:ext>
                       </c:extLst>
                       <c:numCache>
                         <c:formatCode>General</c:formatCode>
-                        <c:ptCount val="5"/>
+                        <c:ptCount val="1"/>
+                        <c:pt idx="0">
+                          <c:v>1</c:v>
+                        </c:pt>
                       </c:numCache>
                     </c:numRef>
                   </c:minus>
@@ -10998,10 +11013,10 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.64</c:v>
+                  <c:v>15.639999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.079999999999998</c:v>
+                  <c:v>19.080000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>13.76</c:v>
@@ -20027,13 +20042,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>107758</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>87320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>96674</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>123151</xdr:rowOff>
@@ -20074,7 +20089,7 @@
       <xdr:rowOff>101889</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>378286</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>49838</xdr:rowOff>
@@ -20115,7 +20130,7 @@
       <xdr:rowOff>111414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>654511</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>59363</xdr:rowOff>
@@ -20156,7 +20171,7 @@
       <xdr:rowOff>111414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>654511</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>59363</xdr:rowOff>
@@ -20197,7 +20212,7 @@
       <xdr:rowOff>111414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>654511</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>59363</xdr:rowOff>
@@ -20238,7 +20253,7 @@
       <xdr:rowOff>111414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>654511</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>59363</xdr:rowOff>
@@ -20279,7 +20294,7 @@
       <xdr:rowOff>101889</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>378286</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>49838</xdr:rowOff>
@@ -20320,7 +20335,7 @@
       <xdr:rowOff>159039</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>235411</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>106988</xdr:rowOff>
@@ -20355,13 +20370,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>107758</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>87320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>96674</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>123151</xdr:rowOff>
@@ -20478,13 +20493,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>545689</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>534605</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>166944</xdr:rowOff>
@@ -20519,13 +20534,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>449344</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>438260</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>35565</xdr:rowOff>
@@ -20560,13 +20575,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>440586</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>429502</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>35565</xdr:rowOff>
@@ -20601,13 +20616,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>388034</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>376950</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>9289</xdr:rowOff>
@@ -20648,7 +20663,7 @@
       <xdr:rowOff>111414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>654511</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>59363</xdr:rowOff>
@@ -20937,70 +20952,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:AA48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="13" width="9.625" customWidth="1"/>
-    <col min="14" max="28" width="9.625" style="31" customWidth="1"/>
-    <col min="29" max="29" width="9.625" customWidth="1"/>
+    <col min="5" max="12" width="9.625" customWidth="1"/>
+    <col min="13" max="27" width="9.625" style="30" customWidth="1"/>
+    <col min="28" max="28" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15" customHeight="1">
-      <c r="A1" s="32"/>
-      <c r="B1" s="33" t="s">
+    <row r="1" spans="1:27" ht="15" customHeight="1">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="L1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="36" t="s">
+    </row>
+    <row r="2" spans="1:27" ht="15" customHeight="1">
+      <c r="A2" s="31" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="B2" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>1.5</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="29">
         <v>1.6</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="36">
         <v>1.8</v>
       </c>
       <c r="F2" s="4">
@@ -21024,793 +21036,740 @@
       <c r="L2" s="4">
         <v>2.4</v>
       </c>
-      <c r="M2" s="39">
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+    </row>
+    <row r="3" spans="1:27" ht="15" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="29">
+        <v>3.4</v>
+      </c>
+      <c r="D3" s="29">
+        <v>3.5</v>
+      </c>
+      <c r="E3" s="36">
+        <v>3.8</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="J3" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="K3" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L3" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="38"/>
+    </row>
+    <row r="4" spans="1:27" s="11" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="D4" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E4" s="17">
+        <v>5.3</v>
+      </c>
+      <c r="F4" s="27">
+        <v>5.7</v>
+      </c>
+      <c r="G4" s="27">
+        <v>5.6</v>
+      </c>
+      <c r="H4" s="27">
+        <v>5.6</v>
+      </c>
+      <c r="I4" s="27">
+        <v>6</v>
+      </c>
+      <c r="J4" s="27">
+        <v>5.8</v>
+      </c>
+      <c r="K4" s="27">
+        <v>6.2</v>
+      </c>
+      <c r="L4" s="27">
+        <v>6.1</v>
+      </c>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="37"/>
+      <c r="V4" s="37"/>
+      <c r="W4" s="37"/>
+      <c r="X4" s="37"/>
+      <c r="Y4" s="37"/>
+      <c r="Z4" s="37"/>
+      <c r="AA4" s="37"/>
+    </row>
+    <row r="5" spans="1:27" s="30" customFormat="1" ht="15" customHeight="1"/>
+    <row r="6" spans="1:27" s="30" customFormat="1" ht="15" customHeight="1"/>
+    <row r="7" spans="1:27" s="30" customFormat="1"/>
+    <row r="8" spans="1:27">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="50"/>
+      <c r="G8" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="52"/>
+      <c r="I8" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="52"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+    </row>
+    <row r="9" spans="1:27" ht="28.5" customHeight="1">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+    </row>
+    <row r="10" spans="1:27" ht="27" customHeight="1">
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="41">
         <f>AVERAGE(C2:L2)</f>
         <v>2.08</v>
       </c>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-    </row>
-    <row r="3" spans="1:28" ht="15" customHeight="1">
-      <c r="A3" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="30">
-        <v>3.4</v>
-      </c>
-      <c r="D3" s="30">
-        <v>3.5</v>
-      </c>
-      <c r="E3" s="38">
-        <v>3.8</v>
-      </c>
-      <c r="F3" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="G3" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>4</v>
-      </c>
-      <c r="I3" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="J3" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="K3" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L3" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="M3" s="39">
+      <c r="F10" s="41">
+        <f>ROUND(_xlfn.STDEV.S(C2:L2),2)</f>
+        <v>0.37</v>
+      </c>
+      <c r="G10" s="41">
         <f>AVERAGE(C3:L3)</f>
-        <v>4.13</v>
-      </c>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-    </row>
-    <row r="4" spans="1:28" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="D4" s="8">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E4" s="18">
-        <v>5.3</v>
-      </c>
-      <c r="F4" s="28">
-        <v>5.7</v>
-      </c>
-      <c r="G4" s="28">
-        <v>5.6</v>
-      </c>
-      <c r="H4" s="28">
-        <v>5.6</v>
-      </c>
-      <c r="I4" s="28">
-        <v>6</v>
-      </c>
-      <c r="J4" s="28">
-        <v>5.8</v>
-      </c>
-      <c r="K4" s="28">
-        <v>6.2</v>
-      </c>
-      <c r="L4" s="28">
-        <v>6.1</v>
-      </c>
-      <c r="M4" s="39">
+        <v>4.1300000000000008</v>
+      </c>
+      <c r="H10" s="42">
+        <f>ROUND(_xlfn.STDEV.S(C3:L3),2)</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I10" s="41">
         <f>AVERAGE(C4:L4)</f>
         <v>5.61</v>
       </c>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="40"/>
-      <c r="AB4" s="40"/>
-    </row>
-    <row r="5" spans="1:28" s="31" customFormat="1" ht="15" customHeight="1"/>
-    <row r="6" spans="1:28" s="31" customFormat="1" ht="15" customHeight="1"/>
-    <row r="7" spans="1:28" s="31" customFormat="1"/>
-    <row r="8" spans="1:28">
-      <c r="A8" s="31"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="55"/>
-      <c r="I8" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="55"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-    </row>
-    <row r="9" spans="1:28" ht="28.5" customHeight="1">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-    </row>
-    <row r="10" spans="1:28" ht="27" customHeight="1">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44">
-        <f>AVERAGE(C2:L2)</f>
-        <v>2.08</v>
-      </c>
-      <c r="F10" s="44">
-        <f>ROUND(_xlfn.STDEV.S(C2:L2),2)</f>
-        <v>0.37</v>
-      </c>
-      <c r="G10" s="44">
-        <f>AVERAGE(C3:L3)</f>
-        <v>4.13</v>
-      </c>
-      <c r="H10" s="45">
-        <f>ROUND(_xlfn.STDEV.S(C3:L3),2)</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="I10" s="44">
-        <f>AVERAGE(C4:L4)</f>
-        <v>5.61</v>
-      </c>
-      <c r="J10" s="44">
+      <c r="J10" s="41">
         <f>ROUND(_xlfn.STDEV.S(C4:L4),2)</f>
         <v>0.48</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-    </row>
-    <row r="11" spans="1:28">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-    </row>
-    <row r="12" spans="1:28">
-      <c r="A12" s="31"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-    </row>
-    <row r="13" spans="1:28">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-    </row>
-    <row r="14" spans="1:28">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-    </row>
-    <row r="15" spans="1:28">
-      <c r="A15" s="40"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="31"/>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="A16" s="40"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="31"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="40"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="31"/>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="31"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="31"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="31"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="31"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="31"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="31"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="31"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="31"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="31"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="31"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="31"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="31"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="31"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="31"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="31"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="31"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="31"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="31"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="31"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="31"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="31"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="31"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="31"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="31"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="31"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="31"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+    </row>
+    <row r="14" spans="1:27">
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+    </row>
+    <row r="15" spans="1:27">
+      <c r="A15" s="37"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+    </row>
+    <row r="16" spans="1:27">
+      <c r="A16" s="37"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="37"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -21828,16 +21787,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A2:G16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="51" t="s">
-        <v>15</v>
+    <row r="2" spans="1:7" ht="16.5">
+      <c r="A2" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -21857,12 +21816,9 @@
       <c r="G2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.1</v>
       </c>
@@ -21881,13 +21837,9 @@
       <c r="G3" s="4">
         <v>17</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.2</v>
       </c>
@@ -21906,13 +21858,9 @@
       <c r="G4" s="4">
         <v>19.5</v>
       </c>
-      <c r="H4" s="2">
-        <f t="shared" ref="H4:H6" si="0">AVERAGE(C4:G4)</f>
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.3</v>
       </c>
@@ -21931,13 +21879,9 @@
       <c r="G5" s="4">
         <v>7.7</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>9.26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="51"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="48"/>
       <c r="B6" s="3">
         <v>0.5</v>
       </c>
@@ -21956,28 +21900,23 @@
       <c r="G6" s="4">
         <v>3.2</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" si="0"/>
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="61" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="14.45" customHeight="1">
+      <c r="B10" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="58"/>
+      <c r="C11" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="61"/>
-      <c r="C11" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -21985,10 +21924,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="23">
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="22">
         <v>0.1</v>
       </c>
       <c r="C12" s="2">
@@ -21999,13 +21937,12 @@
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="23">
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="22">
         <v>0.2</v>
       </c>
       <c r="C13" s="2">
@@ -22016,13 +21953,12 @@
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>0.45</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="23">
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="22">
         <v>0.3</v>
       </c>
       <c r="C14" s="2">
@@ -22033,13 +21969,12 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>2.36</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="B15" s="23">
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="22">
         <v>0.5</v>
       </c>
       <c r="C15" s="2">
@@ -22050,33 +21985,30 @@
         <f>ROUND(_xlfn.STDEV.S(C6:G6),2)</f>
         <v>4.1399999999999997</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" s="24" t="s">
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="2">
         <f>'Control Pea Shoot'!E8</f>
-        <v>16.920000000000002</v>
+        <v>16.919999999999998</v>
       </c>
       <c r="D16" s="2">
         <f>'Control Pea Shoot'!F8</f>
         <v>1.81</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B10:B11"/>
   </mergeCells>
@@ -22087,27 +22019,27 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="24" width="9.625" customWidth="1"/>
+    <col min="5" max="23" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="1:7" ht="15" customHeight="1">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -22116,16 +22048,13 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>13</v>
+    </row>
+    <row r="2" spans="1:7" s="11" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="8">
         <v>11</v>
@@ -22133,41 +22062,37 @@
       <c r="D2" s="8">
         <v>11.6</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>11.6</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <v>12</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>12.1</v>
       </c>
-      <c r="H2" s="8">
-        <f>AVERAGE(C2:G2)</f>
-        <v>11.66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1"/>
-    <row r="4" spans="1:8" ht="15" customHeight="1"/>
-    <row r="6" spans="1:8">
-      <c r="D6" s="52" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1"/>
+    <row r="4" spans="1:7" ht="15" customHeight="1"/>
+    <row r="6" spans="1:7">
+      <c r="D6" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="56"/>
+    </row>
+    <row r="7" spans="1:7" ht="28.5" customHeight="1">
+      <c r="D7" s="49"/>
+      <c r="E7" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="59"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.5" customHeight="1">
-      <c r="D7" s="52"/>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" customHeight="1">
+    <row r="8" spans="1:7" ht="27" customHeight="1">
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
@@ -22180,41 +22105,41 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="12"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="12"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="12"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+    <row r="13" spans="1:7">
+      <c r="A13" s="11"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="11"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="11"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -22227,16 +22152,16 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:9" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -22256,12 +22181,9 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -22280,13 +22202,9 @@
       <c r="G2" s="4">
         <v>12.9</v>
       </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -22305,13 +22223,9 @@
       <c r="G3" s="4">
         <v>15.5</v>
       </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H5" si="0">AVERAGE(C3:G3)</f>
-        <v>15.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -22330,13 +22244,9 @@
       <c r="G4" s="4">
         <v>18</v>
       </c>
-      <c r="H4" s="2">
-        <f t="shared" si="0"/>
-        <v>19.079999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -22355,38 +22265,28 @@
       <c r="G5" s="4">
         <v>14.3</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>13.76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:9"/>
+    <row r="8" spans="1:9"/>
+    <row r="9" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:9" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
@@ -22398,51 +22298,47 @@
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>1.29</v>
       </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="12" spans="1:9" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" ref="C12:C14" si="1">AVERAGE(C3:G3)</f>
-        <v>15.64</v>
+        <f t="shared" ref="C12:C14" si="0">AVERAGE(C3:G3)</f>
+        <v>15.639999999999997</v>
       </c>
       <c r="D12" s="2">
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>1.88</v>
       </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="13" spans="1:9" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="1"/>
-        <v>19.079999999999998</v>
+        <f t="shared" si="0"/>
+        <v>19.080000000000002</v>
       </c>
       <c r="D13" s="2">
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>1.33</v>
       </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="14" spans="1:9" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>13.76</v>
       </c>
       <c r="D14" s="2">
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>3.22</v>
       </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:10">
+    </row>
+    <row r="15" spans="1:9">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
@@ -22454,26 +22350,19 @@
         <f>'Control Pea Root'!F8</f>
         <v>0.43</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="8:15">
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="8:15">
-      <c r="H18" s="7"/>
-    </row>
-    <row r="21" spans="8:15">
-      <c r="O21">
+    </row>
+    <row r="16" spans="1:9"/>
+    <row r="17" spans="14:14"/>
+    <row r="18" spans="14:14"/>
+    <row r="21" spans="14:14">
+      <c r="N21">
         <f>19.08/14.9</f>
-        <v>1.2805369127516799</v>
+        <v>1.2805369127516777</v>
       </c>
     </row>
   </sheetData>
@@ -22489,16 +22378,16 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:7" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -22518,12 +22407,9 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:7" ht="13.5">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -22542,13 +22428,9 @@
       <c r="G2" s="4">
         <v>14</v>
       </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:7" ht="13.5">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -22567,13 +22449,9 @@
       <c r="G3" s="4">
         <v>11</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:7" ht="13.5">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -22592,13 +22470,9 @@
       <c r="G4" s="4">
         <v>14</v>
       </c>
-      <c r="H4" s="2">
-        <f>AVERAGE(C4:G4)</f>
-        <v>14.68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:7" ht="13.5">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -22617,38 +22491,28 @@
       <c r="G5" s="4">
         <v>6.3</v>
       </c>
-      <c r="H5" s="2">
-        <f>AVERAGE(C5:G5)</f>
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="H8" s="11"/>
-    </row>
-    <row r="9" spans="1:8" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="13.5"/>
+    <row r="8" spans="1:7" ht="13.5"/>
+    <row r="9" spans="1:7" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:7" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
@@ -22660,9 +22524,8 @@
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>1.78</v>
       </c>
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" spans="1:8" ht="14.45" customHeight="1">
+    </row>
+    <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
@@ -22675,21 +22538,20 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="14.45" customHeight="1">
+    <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
       <c r="C13" s="2">
         <f>AVERAGE(C4:G4)</f>
-        <v>14.68</v>
+        <v>14.680000000000001</v>
       </c>
       <c r="D13" s="2">
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>3.33</v>
       </c>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" ht="14.45" customHeight="1">
+    </row>
+    <row r="14" spans="1:7" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
@@ -22701,9 +22563,8 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>1.1399999999999999</v>
       </c>
-      <c r="H14" s="11"/>
-    </row>
-    <row r="15" spans="1:8">
+    </row>
+    <row r="15" spans="1:7" ht="13.5">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
@@ -22715,17 +22576,12 @@
         <f>'Control Pea Root'!F8</f>
         <v>0.43</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="11"/>
-    </row>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:7" ht="13.5"/>
+    <row r="17" ht="13.5"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:D9"/>
@@ -22739,16 +22595,16 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:9" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -22768,12 +22624,9 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -22792,13 +22645,9 @@
       <c r="G2" s="4">
         <v>14.8</v>
       </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>15.24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -22817,13 +22666,9 @@
       <c r="G3" s="4">
         <v>15.3</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>15.08</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -22842,13 +22687,9 @@
       <c r="G4" s="4">
         <v>12.5</v>
       </c>
-      <c r="H4" s="2">
-        <f>AVERAGE(C4:G4)</f>
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -22867,38 +22708,28 @@
       <c r="G5" s="4">
         <v>12</v>
       </c>
-      <c r="H5" s="2">
-        <f>AVERAGE(C5:G5)</f>
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:9"/>
+    <row r="8" spans="1:9"/>
+    <row r="9" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:9" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
@@ -22910,23 +22741,21 @@
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>1.39</v>
       </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="12" spans="1:9" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
       <c r="C12" s="2">
         <f>AVERAGE(C3:G3)</f>
-        <v>15.08</v>
+        <v>15.080000000000002</v>
       </c>
       <c r="D12" s="2">
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>1.75</v>
       </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="13" spans="1:9" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
@@ -22938,9 +22767,8 @@
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>5.57</v>
       </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="14" spans="1:9" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
@@ -22952,9 +22780,8 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>1.57</v>
       </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:10">
+    </row>
+    <row r="15" spans="1:9">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
@@ -22966,22 +22793,15 @@
         <f>'Control Pea Root'!F8</f>
         <v>0.43</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18" s="7"/>
-    </row>
+    </row>
+    <row r="16" spans="1:9"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:D9"/>
@@ -22995,16 +22815,16 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:9" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -23024,12 +22844,9 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -23048,13 +22865,9 @@
       <c r="G2" s="4">
         <v>14.5</v>
       </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -23073,13 +22886,9 @@
       <c r="G3" s="4">
         <v>14</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -23098,13 +22907,9 @@
       <c r="G4" s="4">
         <v>13.3</v>
       </c>
-      <c r="H4" s="2">
-        <f>AVERAGE(C4:G4)</f>
-        <v>14.72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -23123,38 +22928,28 @@
       <c r="G5" s="4">
         <v>6.3</v>
       </c>
-      <c r="H5" s="2">
-        <f>AVERAGE(C5:G5)</f>
-        <v>11.68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:9"/>
+    <row r="8" spans="1:9"/>
+    <row r="9" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:9" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
@@ -23166,9 +22961,8 @@
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>0.82</v>
       </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="12" spans="1:9" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
@@ -23180,37 +22974,34 @@
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>0.91</v>
       </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="13" spans="1:9" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
       <c r="C13" s="2">
         <f>AVERAGE(C4:G4)</f>
-        <v>14.72</v>
+        <v>14.720000000000002</v>
       </c>
       <c r="D13" s="2">
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>3.89</v>
       </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="14" spans="1:9" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
       <c r="C14" s="2">
         <f>AVERAGE(C5:G5)</f>
-        <v>11.68</v>
+        <v>11.679999999999998</v>
       </c>
       <c r="D14" s="2">
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>4.59</v>
       </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:10">
+    </row>
+    <row r="15" spans="1:9">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
@@ -23222,22 +23013,15 @@
         <f>'Control Pea Root'!F8</f>
         <v>0.43</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18" s="7"/>
-    </row>
+    </row>
+    <row r="16" spans="1:9"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:D9"/>
@@ -23251,27 +23035,27 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="24" width="9.625" customWidth="1"/>
+    <col min="5" max="23" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="1:7" ht="15" customHeight="1">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -23280,16 +23064,13 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>13</v>
+    </row>
+    <row r="2" spans="1:7" s="11" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="8">
         <v>30</v>
@@ -23297,88 +23078,84 @@
       <c r="D2" s="8">
         <v>31</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>32</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <v>31.8</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>32</v>
       </c>
-      <c r="H2" s="8">
-        <f>AVERAGE(C2:G2)</f>
-        <v>31.36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1"/>
-    <row r="4" spans="1:8" ht="15" customHeight="1"/>
-    <row r="6" spans="1:8">
-      <c r="D6" s="52" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1"/>
+    <row r="4" spans="1:7" ht="15" customHeight="1"/>
+    <row r="6" spans="1:7">
+      <c r="D6" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="56"/>
+    </row>
+    <row r="7" spans="1:7" ht="28.5" customHeight="1">
+      <c r="D7" s="49"/>
+      <c r="E7" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="59"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.5" customHeight="1">
-      <c r="D7" s="52"/>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" customHeight="1">
+    <row r="8" spans="1:7" ht="27" customHeight="1">
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="2">
         <f>AVERAGE(C2:G2)</f>
-        <v>31.36</v>
+        <v>31.360000000000003</v>
       </c>
       <c r="F8" s="2">
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>0.86</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="12"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="12"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="12"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+    <row r="13" spans="1:7">
+      <c r="A13" s="11"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="11"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="11"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -23391,16 +23168,16 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:9" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -23420,12 +23197,9 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -23444,13 +23218,9 @@
       <c r="G2" s="4">
         <v>33</v>
       </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>34.200000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -23469,13 +23239,9 @@
       <c r="G3" s="4">
         <v>35</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>33.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -23494,13 +23260,9 @@
       <c r="G4" s="4">
         <v>22</v>
       </c>
-      <c r="H4" s="2">
-        <f>AVERAGE(C4:G4)</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -23519,37 +23281,28 @@
       <c r="G5" s="4">
         <v>20</v>
       </c>
-      <c r="H5" s="2">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:9"/>
+    <row r="8" spans="1:9"/>
+    <row r="9" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:9" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
@@ -23561,9 +23314,8 @@
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="12" spans="1:9" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
@@ -23575,9 +23327,8 @@
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>0.82</v>
       </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="13" spans="1:9" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
@@ -23589,9 +23340,8 @@
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>6.32</v>
       </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="14" spans="1:9" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
@@ -23603,36 +23353,28 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>6.73</v>
       </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:10">
+    </row>
+    <row r="15" spans="1:9">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="8">
         <f>'Control Pea Total Length'!E8</f>
-        <v>31.36</v>
+        <v>31.360000000000003</v>
       </c>
       <c r="D15" s="9">
         <f>'Control Pea Total Length'!F8</f>
         <v>0.86</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18" s="7"/>
-    </row>
+    </row>
+    <row r="16" spans="1:9"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:D9"/>
@@ -23646,16 +23388,16 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:9" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -23675,12 +23417,9 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -23699,13 +23438,9 @@
       <c r="G2" s="4">
         <v>37.5</v>
       </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -23724,13 +23459,9 @@
       <c r="G3" s="4">
         <v>34.5</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>35.200000000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -23749,13 +23480,9 @@
       <c r="G4" s="4">
         <v>30</v>
       </c>
-      <c r="H4" s="2">
-        <f>AVERAGE(C4:G4)</f>
-        <v>30.02</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -23774,38 +23501,28 @@
       <c r="G5" s="4">
         <v>17</v>
       </c>
-      <c r="H5" s="2">
-        <f>AVERAGE(C5:G5)</f>
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:9"/>
+    <row r="8" spans="1:9"/>
+    <row r="9" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:9" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
@@ -23817,9 +23534,8 @@
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>1</v>
       </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="12" spans="1:9" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
@@ -23831,9 +23547,8 @@
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>3.87</v>
       </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="13" spans="1:9" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
@@ -23845,9 +23560,8 @@
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>6.35</v>
       </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="14" spans="1:9" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
@@ -23859,36 +23573,28 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>3.36</v>
       </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:10">
+    </row>
+    <row r="15" spans="1:9">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="8">
         <f>'Control Pea Total Length'!E8</f>
-        <v>31.36</v>
+        <v>31.360000000000003</v>
       </c>
       <c r="D15" s="9">
         <f>'Control Pea Total Length'!F8</f>
         <v>0.86</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18" s="7"/>
-    </row>
+    </row>
+    <row r="16" spans="1:9"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:D9"/>
@@ -23902,16 +23608,16 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:7" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -23931,12 +23637,9 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:7" ht="13.5">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -23955,13 +23658,9 @@
       <c r="G2" s="4">
         <v>35</v>
       </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:7" ht="13.5">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -23980,13 +23679,9 @@
       <c r="G3" s="4">
         <v>32</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>35.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:7" ht="13.5">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -24005,13 +23700,9 @@
       <c r="G4" s="4">
         <v>26.7</v>
       </c>
-      <c r="H4" s="2">
-        <f>AVERAGE(C4:G4)</f>
-        <v>28.28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:7" ht="13.5">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -24030,38 +23721,28 @@
       <c r="G5" s="4">
         <v>13.6</v>
       </c>
-      <c r="H5" s="2">
-        <f>AVERAGE(C5:G5)</f>
-        <v>17.399999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="H8" s="11"/>
-    </row>
-    <row r="9" spans="1:8" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="13.5"/>
+    <row r="8" spans="1:7" ht="13.5"/>
+    <row r="9" spans="1:7" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:7" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
@@ -24073,9 +23754,8 @@
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>1.73</v>
       </c>
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" spans="1:8" ht="14.45" customHeight="1">
+    </row>
+    <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
@@ -24088,7 +23768,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="14.45" customHeight="1">
+    <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
@@ -24100,9 +23780,8 @@
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>4.72</v>
       </c>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" ht="14.45" customHeight="1">
+    </row>
+    <row r="14" spans="1:7" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
@@ -24114,31 +23793,25 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>3.05</v>
       </c>
-      <c r="H14" s="11"/>
-    </row>
-    <row r="15" spans="1:8">
+    </row>
+    <row r="15" spans="1:7" ht="13.5">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="8">
         <f>'Control Pea Total Length'!E8</f>
-        <v>31.36</v>
+        <v>31.360000000000003</v>
       </c>
       <c r="D15" s="9">
         <f>'Control Pea Total Length'!F8</f>
         <v>0.86</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="11"/>
-    </row>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:7" ht="13.5"/>
+    <row r="17" ht="13.5"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:D9"/>
@@ -24152,16 +23825,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AK26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:AJ26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>12</v>
+    <row r="1" spans="1:36" ht="15" customHeight="1">
+      <c r="A1" s="48" t="s">
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -24196,12 +23869,9 @@
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" ht="15" customHeight="1">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:36" ht="15" customHeight="1">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -24235,36 +23905,32 @@
       <c r="L2" s="4">
         <v>0</v>
       </c>
-      <c r="M2" s="4">
-        <f>AVERAGE(C2:L2)</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="12"/>
-    </row>
-    <row r="3" spans="1:37" ht="15" customHeight="1">
-      <c r="A3" s="51"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+    </row>
+    <row r="3" spans="1:36" ht="15" customHeight="1">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -24298,36 +23964,32 @@
       <c r="L3" s="4">
         <v>1.6</v>
       </c>
-      <c r="M3" s="4">
-        <f>AVERAGE(C3:L3)</f>
-        <v>2.37</v>
-      </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-      <c r="AJ3" s="11"/>
-      <c r="AK3" s="11"/>
-    </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1">
-      <c r="A4" s="51"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+    </row>
+    <row r="4" spans="1:36" ht="15" customHeight="1">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -24361,13 +24023,9 @@
       <c r="L4" s="4">
         <v>2.1</v>
       </c>
-      <c r="M4" s="4">
-        <f>AVERAGE(C4:L4)</f>
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" ht="15" customHeight="1">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:36" ht="15" customHeight="1">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -24401,14 +24059,10 @@
       <c r="L5" s="4">
         <v>2.1</v>
       </c>
-      <c r="M5" s="4">
-        <f>AVERAGE(C5:L5)</f>
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
-      <c r="A7" s="51" t="s">
-        <v>14</v>
+    </row>
+    <row r="7" spans="1:36" ht="16.5">
+      <c r="A7" s="48" t="s">
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -24443,12 +24097,9 @@
       <c r="L7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
-      <c r="A8" s="51"/>
+    </row>
+    <row r="8" spans="1:36">
+      <c r="A8" s="48"/>
       <c r="B8" s="3">
         <v>0.1</v>
       </c>
@@ -24482,13 +24133,9 @@
       <c r="L8" s="4">
         <v>0</v>
       </c>
-      <c r="M8" s="4">
-        <f>C8+D8+E8+F8+G8+H8+I8+J8+K8+L8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
-      <c r="A9" s="51"/>
+    </row>
+    <row r="9" spans="1:36">
+      <c r="A9" s="48"/>
       <c r="B9" s="3">
         <v>0.2</v>
       </c>
@@ -24522,13 +24169,9 @@
       <c r="L9" s="4">
         <v>5.7</v>
       </c>
-      <c r="M9" s="4">
-        <f>AVERAGE(C9:L9)</f>
-        <v>5.14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37">
-      <c r="A10" s="51"/>
+    </row>
+    <row r="10" spans="1:36">
+      <c r="A10" s="48"/>
       <c r="B10" s="3">
         <v>0.3</v>
       </c>
@@ -24562,13 +24205,9 @@
       <c r="L10" s="4">
         <v>4.9000000000000004</v>
       </c>
-      <c r="M10" s="4">
-        <f>AVERAGE(C10:L10)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="A11" s="51"/>
+    </row>
+    <row r="11" spans="1:36">
+      <c r="A11" s="48"/>
       <c r="B11" s="3">
         <v>0.5</v>
       </c>
@@ -24602,14 +24241,10 @@
       <c r="L11" s="4">
         <v>5.9</v>
       </c>
-      <c r="M11" s="4">
-        <f>AVERAGE(C11:L11)</f>
-        <v>5.54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37">
-      <c r="A13" s="51" t="s">
-        <v>15</v>
+    </row>
+    <row r="13" spans="1:36" ht="16.5">
+      <c r="A13" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>18</v>
@@ -24644,12 +24279,9 @@
       <c r="L13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37">
-      <c r="A14" s="51"/>
+    </row>
+    <row r="14" spans="1:36">
+      <c r="A14" s="48"/>
       <c r="B14" s="3">
         <v>0.1</v>
       </c>
@@ -24683,13 +24315,9 @@
       <c r="L14" s="4">
         <v>0</v>
       </c>
-      <c r="M14" s="4">
-        <f>AVERAGE(C14:L14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37">
-      <c r="A15" s="51"/>
+    </row>
+    <row r="15" spans="1:36">
+      <c r="A15" s="48"/>
       <c r="B15" s="3">
         <v>0.2</v>
       </c>
@@ -24723,13 +24351,9 @@
       <c r="L15" s="4">
         <v>6</v>
       </c>
-      <c r="M15" s="4">
-        <f>AVERAGE(C15:L15)</f>
-        <v>6.36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="A16" s="51"/>
+    </row>
+    <row r="16" spans="1:36">
+      <c r="A16" s="48"/>
       <c r="B16" s="3">
         <v>0.3</v>
       </c>
@@ -24763,13 +24387,9 @@
       <c r="L16" s="4">
         <v>6.8</v>
       </c>
-      <c r="M16" s="4">
-        <f>AVERAGE(C16:L16)</f>
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="51"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="48"/>
       <c r="B17" s="3">
         <v>0.5</v>
       </c>
@@ -24803,53 +24423,49 @@
       <c r="L17" s="4">
         <v>7.7</v>
       </c>
-      <c r="M17" s="4">
-        <f>AVERAGE(C17:L17)</f>
-        <v>7.54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="6.6" customHeight="1"/>
-    <row r="19" spans="1:13" ht="6.6" customHeight="1"/>
-    <row r="20" spans="1:13">
-      <c r="B20" s="58" t="s">
+    </row>
+    <row r="18" spans="1:12" ht="6.6" customHeight="1"/>
+    <row r="19" spans="1:12" ht="6.6" customHeight="1"/>
+    <row r="20" spans="1:12">
+      <c r="B20" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="54"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="B21" s="55"/>
+      <c r="C21" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="57"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="B21" s="58"/>
-      <c r="C21" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="29" t="s">
+      <c r="E21" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="29" t="s">
+      <c r="G21" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="B22" s="30">
+    <row r="22" spans="1:12">
+      <c r="B22" s="29">
         <v>0.1</v>
       </c>
       <c r="C22" s="8">
@@ -24877,8 +24493,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="B23" s="30">
+    <row r="23" spans="1:12">
+      <c r="B23" s="29">
         <v>0.2</v>
       </c>
       <c r="C23" s="8">
@@ -24906,13 +24522,13 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="B24" s="30">
+    <row r="24" spans="1:12">
+      <c r="B24" s="29">
         <v>0.3</v>
       </c>
       <c r="C24" s="8">
         <f>AVERAGE(C4:L4)</f>
-        <v>2.19</v>
+        <v>2.1900000000000004</v>
       </c>
       <c r="D24" s="8">
         <f>ROUND(_xlfn.STDEV.S(C4:L4),2)</f>
@@ -24928,20 +24544,20 @@
       </c>
       <c r="G24" s="8">
         <f>AVERAGE(C16:L16)</f>
-        <v>7.39</v>
+        <v>7.3899999999999988</v>
       </c>
       <c r="H24" s="8">
         <f>ROUND(_xlfn.STDEV.S(C16:L16),2)</f>
         <v>0.45</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="B25" s="30">
+    <row r="25" spans="1:12">
+      <c r="B25" s="29">
         <v>0.5</v>
       </c>
       <c r="C25" s="8">
         <f>AVERAGE(C5:L5)</f>
-        <v>2.58</v>
+        <v>2.5800000000000005</v>
       </c>
       <c r="D25" s="8">
         <f>ROUND(_xlfn.STDEV.S(C5:L5),2)</f>
@@ -24957,14 +24573,14 @@
       </c>
       <c r="G25" s="8">
         <f>AVERAGE(C17:L17)</f>
-        <v>7.54</v>
+        <v>7.5400000000000009</v>
       </c>
       <c r="H25" s="8">
         <f>ROUND(_xlfn.STDEV.S(C17:L17),2)</f>
         <v>0.54</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:12">
       <c r="B26" s="8" t="s">
         <v>0</v>
       </c>
@@ -24978,7 +24594,7 @@
       </c>
       <c r="E26" s="8">
         <f>'Control Onion'!G10</f>
-        <v>4.13</v>
+        <v>4.1300000000000008</v>
       </c>
       <c r="F26" s="8">
         <f>'Control Onion'!H10</f>
@@ -25005,7 +24621,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="M9:M17 M2:M7 C23:H25 D22:H22" formulaRange="1"/>
+    <ignoredError sqref="C23:H25 D22:H22" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -25013,16 +24629,16 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="37" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="51" t="s">
-        <v>15</v>
+    <row r="1" spans="1:8" ht="16.5">
+      <c r="A1" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -25039,15 +24655,9 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -25063,16 +24673,9 @@
       <c r="F2" s="4">
         <v>32.6</v>
       </c>
-      <c r="G2" s="4">
-        <v>37.9</v>
-      </c>
-      <c r="H2" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>35.799999999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -25088,16 +24691,9 @@
       <c r="F3" s="4">
         <v>31</v>
       </c>
-      <c r="G3" s="4">
-        <v>33.5</v>
-      </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H5" si="0">AVERAGE(C3:G3)</f>
-        <v>36.58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -25113,16 +24709,9 @@
       <c r="F4" s="4">
         <v>37.5</v>
       </c>
-      <c r="G4" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" si="0"/>
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -25138,124 +24727,99 @@
       <c r="F5" s="4">
         <v>32</v>
       </c>
-      <c r="G5" s="4">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>26.88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B9" s="52" t="s">
+    </row>
+    <row r="7" spans="1:8"/>
+    <row r="8" spans="1:8"/>
+    <row r="9" spans="1:8" ht="14.45" customHeight="1">
+      <c r="B9" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="47"/>
+    </row>
+    <row r="10" spans="1:8" ht="14.45" customHeight="1">
+      <c r="B10" s="49"/>
+      <c r="C10" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B10" s="52"/>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.45" customHeight="1">
+    </row>
+    <row r="11" spans="1:8" ht="14.45" customHeight="1">
       <c r="B11" s="3">
         <v>0.1</v>
       </c>
       <c r="C11" s="2">
-        <f>AVERAGE(C2:G2)</f>
-        <v>35.799999999999997</v>
+        <f>AVERAGE(C2:F2)</f>
+        <v>35.274999999999999</v>
       </c>
       <c r="D11" s="2">
-        <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
-        <v>2.12</v>
-      </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.45" customHeight="1">
+        <f>ROUND(_xlfn.STDEV.S(C2:F2),2)</f>
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.45" customHeight="1">
       <c r="B12" s="3">
         <v>0.2</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" ref="C12:C14" si="1">AVERAGE(C3:G3)</f>
-        <v>36.58</v>
+        <f>AVERAGE(C3:F3)</f>
+        <v>37.35</v>
       </c>
       <c r="D12" s="2">
-        <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
-        <v>4.12</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1">
+        <f>ROUND(_xlfn.STDEV.S(C3:F3),2)</f>
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.45" customHeight="1">
       <c r="B13" s="3">
         <v>0.3</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="1"/>
-        <v>34.4</v>
+        <f>AVERAGE(C4:F4)</f>
+        <v>35.375</v>
       </c>
       <c r="D13" s="2">
-        <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
-        <v>2.72</v>
-      </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.45" customHeight="1">
+        <f>ROUND(_xlfn.STDEV.S(C4:F4),2)</f>
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.45" customHeight="1">
       <c r="B14" s="3">
         <v>0.5</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="1"/>
-        <v>26.88</v>
+        <f>AVERAGE(C5:F5)</f>
+        <v>27.6</v>
       </c>
       <c r="D14" s="2">
-        <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
-        <v>3.84</v>
-      </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:10">
+        <f>ROUND(_xlfn.STDEV.S(C5:F5),2)</f>
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="8">
         <f>'Control Pea Total Length'!E8</f>
-        <v>31.36</v>
+        <v>31.360000000000003</v>
       </c>
       <c r="D15" s="9">
         <f>'Control Pea Total Length'!F8</f>
         <v>0.86</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18" s="7"/>
-    </row>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C9:D9"/>
@@ -25269,16 +24833,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AK26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:AJ26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>12</v>
+    <row r="1" spans="1:36" ht="15" customHeight="1">
+      <c r="A1" s="48" t="s">
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -25313,12 +24877,9 @@
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" ht="15" customHeight="1">
-      <c r="A2" s="51"/>
+    </row>
+    <row r="2" spans="1:36" ht="15" customHeight="1">
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -25352,36 +24913,32 @@
       <c r="L2" s="4">
         <v>1</v>
       </c>
-      <c r="M2" s="4">
-        <f>AVERAGE(C2:L2)</f>
-        <v>1.26</v>
-      </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="12"/>
-    </row>
-    <row r="3" spans="1:37" ht="15" customHeight="1">
-      <c r="A3" s="51"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+    </row>
+    <row r="3" spans="1:36" ht="15" customHeight="1">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -25415,36 +24972,32 @@
       <c r="L3" s="4">
         <v>1.2</v>
       </c>
-      <c r="M3" s="4">
-        <f>AVERAGE(C3:L3)</f>
-        <v>1.5</v>
-      </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-      <c r="AJ3" s="11"/>
-      <c r="AK3" s="11"/>
-    </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1">
-      <c r="A4" s="51"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+    </row>
+    <row r="4" spans="1:36" ht="15" customHeight="1">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -25478,13 +25031,9 @@
       <c r="L4" s="4">
         <v>2.1</v>
       </c>
-      <c r="M4" s="4">
-        <f>AVERAGE(C4:L4)</f>
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" ht="15" customHeight="1">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:36" ht="15" customHeight="1">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -25518,14 +25067,10 @@
       <c r="L5" s="4">
         <v>2.7</v>
       </c>
-      <c r="M5" s="4">
-        <f>AVERAGE(C5:L5)</f>
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
-      <c r="A7" s="51" t="s">
-        <v>14</v>
+    </row>
+    <row r="7" spans="1:36" ht="16.5">
+      <c r="A7" s="48" t="s">
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -25560,12 +25105,9 @@
       <c r="L7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
-      <c r="A8" s="51"/>
+    </row>
+    <row r="8" spans="1:36">
+      <c r="A8" s="48"/>
       <c r="B8" s="3">
         <v>0.1</v>
       </c>
@@ -25599,13 +25141,9 @@
       <c r="L8" s="4">
         <v>1.6</v>
       </c>
-      <c r="M8" s="4">
-        <f>AVERAGE(C8:L8)</f>
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
-      <c r="A9" s="51"/>
+    </row>
+    <row r="9" spans="1:36">
+      <c r="A9" s="48"/>
       <c r="B9" s="3">
         <v>0.2</v>
       </c>
@@ -25639,13 +25177,9 @@
       <c r="L9" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M9" s="4">
-        <f>AVERAGE(C9:L9)</f>
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37">
-      <c r="A10" s="51"/>
+    </row>
+    <row r="10" spans="1:36">
+      <c r="A10" s="48"/>
       <c r="B10" s="3">
         <v>0.3</v>
       </c>
@@ -25679,13 +25213,9 @@
       <c r="L10" s="4">
         <v>3.5</v>
       </c>
-      <c r="M10" s="4">
-        <f>AVERAGE(C10:L10)</f>
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="A11" s="51"/>
+    </row>
+    <row r="11" spans="1:36">
+      <c r="A11" s="48"/>
       <c r="B11" s="3">
         <v>0.5</v>
       </c>
@@ -25719,14 +25249,10 @@
       <c r="L11" s="4">
         <v>6.3</v>
       </c>
-      <c r="M11" s="4">
-        <f>AVERAGE(C11:L11)</f>
-        <v>5.69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37">
-      <c r="A13" s="51" t="s">
-        <v>15</v>
+    </row>
+    <row r="13" spans="1:36" ht="16.5">
+      <c r="A13" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>18</v>
@@ -25761,12 +25287,9 @@
       <c r="L13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37">
-      <c r="A14" s="51"/>
+    </row>
+    <row r="14" spans="1:36">
+      <c r="A14" s="48"/>
       <c r="B14" s="3">
         <v>0.1</v>
       </c>
@@ -25800,13 +25323,9 @@
       <c r="L14" s="4">
         <v>2.1</v>
       </c>
-      <c r="M14" s="4">
-        <f>AVERAGE(C14:L14)</f>
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37">
-      <c r="A15" s="51"/>
+    </row>
+    <row r="15" spans="1:36">
+      <c r="A15" s="48"/>
       <c r="B15" s="3">
         <v>0.2</v>
       </c>
@@ -25840,13 +25359,9 @@
       <c r="L15" s="4">
         <v>3.4</v>
       </c>
-      <c r="M15" s="4">
-        <f>AVERAGE(C15:L15)</f>
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="A16" s="51"/>
+    </row>
+    <row r="16" spans="1:36">
+      <c r="A16" s="48"/>
       <c r="B16" s="3">
         <v>0.3</v>
       </c>
@@ -25880,13 +25395,9 @@
       <c r="L16" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="M16" s="4">
-        <f>AVERAGE(C16:L16)</f>
-        <v>4.88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="51"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="48"/>
       <c r="B17" s="3">
         <v>0.5</v>
       </c>
@@ -25920,58 +25431,54 @@
       <c r="L17" s="4">
         <v>6</v>
       </c>
-      <c r="M17" s="4">
-        <f>AVERAGE(C17:L17)</f>
-        <v>7.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="6.6" customHeight="1"/>
-    <row r="19" spans="1:13" ht="6.6" customHeight="1"/>
-    <row r="20" spans="1:13">
-      <c r="B20" s="52" t="s">
+    </row>
+    <row r="18" spans="1:12" ht="6.6" customHeight="1"/>
+    <row r="19" spans="1:12" ht="6.6" customHeight="1"/>
+    <row r="20" spans="1:12">
+      <c r="B20" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="47"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="B21" s="49"/>
+      <c r="C21" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="50"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="B21" s="52"/>
-      <c r="C21" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:12">
       <c r="B22" s="3">
         <v>0.1</v>
       </c>
       <c r="C22" s="2">
         <f>AVERAGE(C2:L2)</f>
-        <v>1.26</v>
+        <v>1.2600000000000002</v>
       </c>
       <c r="D22" s="2">
         <f>ROUND(_xlfn.STDEV.S(C2:L2),2)</f>
@@ -25979,7 +25486,7 @@
       </c>
       <c r="E22" s="2">
         <f>AVERAGE(C8:L8)</f>
-        <v>2.35</v>
+        <v>2.3500000000000005</v>
       </c>
       <c r="F22" s="2">
         <f>ROUND(_xlfn.STDEV.S(C8:L8),2)</f>
@@ -25987,14 +25494,14 @@
       </c>
       <c r="G22" s="2">
         <f>AVERAGE(C14:L14)</f>
-        <v>3.24</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="H22" s="2">
         <f>ROUND(_xlfn.STDEV.S(C14:L14),2)</f>
         <v>0.86</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:12">
       <c r="B23" s="3">
         <v>0.2</v>
       </c>
@@ -26008,7 +25515,7 @@
       </c>
       <c r="E23" s="2">
         <f>AVERAGE(C9:L9)</f>
-        <v>2.92</v>
+        <v>2.9200000000000004</v>
       </c>
       <c r="F23" s="2">
         <f>ROUND(_xlfn.STDEV.S(C9:L9),2)</f>
@@ -26023,7 +25530,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:12">
       <c r="B24" s="3">
         <v>0.3</v>
       </c>
@@ -26037,7 +25544,7 @@
       </c>
       <c r="E24" s="2">
         <f>AVERAGE(C10:L10)</f>
-        <v>3.77</v>
+        <v>3.7700000000000005</v>
       </c>
       <c r="F24" s="2">
         <f>ROUND(_xlfn.STDEV.S(C10:L10),2)</f>
@@ -26045,14 +25552,14 @@
       </c>
       <c r="G24" s="2">
         <f>AVERAGE(C16:L16)</f>
-        <v>4.88</v>
+        <v>4.8800000000000008</v>
       </c>
       <c r="H24" s="2">
         <f>ROUND(_xlfn.STDEV.S(C16:L16),2)</f>
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:12">
       <c r="B25" s="3">
         <v>0.5</v>
       </c>
@@ -26066,7 +25573,7 @@
       </c>
       <c r="E25" s="2">
         <f>AVERAGE(C11:L11)</f>
-        <v>5.69</v>
+        <v>5.6899999999999995</v>
       </c>
       <c r="F25" s="2">
         <f>ROUND(_xlfn.STDEV.S(C11:L11),2)</f>
@@ -26074,14 +25581,14 @@
       </c>
       <c r="G25" s="2">
         <f>AVERAGE(C17:L17)</f>
-        <v>7.16</v>
+        <v>7.1599999999999993</v>
       </c>
       <c r="H25" s="2">
         <f>ROUND(_xlfn.STDEV.S(C17:L17),2)</f>
         <v>1.03</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:12">
       <c r="B26" s="8" t="s">
         <v>0</v>
       </c>
@@ -26095,7 +25602,7 @@
       </c>
       <c r="E26" s="8">
         <f>'Control Onion'!G10</f>
-        <v>4.13</v>
+        <v>4.1300000000000008</v>
       </c>
       <c r="F26" s="8">
         <f>'Control Onion'!H10</f>
@@ -26122,7 +25629,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="M2:M17 C22:H23 C25:H25 C24:E24 G24:H24" formulaRange="1"/>
+    <ignoredError sqref="C22:H23 C25:H25 C24:E24 G24:H24" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -26138,8 +25645,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>12</v>
+      <c r="A1" s="48" t="s">
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -26175,11 +25682,11 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="15" customHeight="1">
-      <c r="A2" s="51"/>
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -26217,32 +25724,32 @@
         <f>AVERAGE(C2:L2)</f>
         <v>2.34</v>
       </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="12"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
     </row>
     <row r="3" spans="1:37" ht="15" customHeight="1">
-      <c r="A3" s="51"/>
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -26280,32 +25787,32 @@
         <f t="shared" ref="M3:M11" si="0">AVERAGE(C3:L3)</f>
         <v>1.93</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-      <c r="AJ3" s="11"/>
-      <c r="AK3" s="11"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
     </row>
     <row r="4" spans="1:37" ht="15" customHeight="1">
-      <c r="A4" s="51"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -26345,7 +25852,7 @@
       </c>
     </row>
     <row r="5" spans="1:37" ht="15" customHeight="1">
-      <c r="A5" s="51"/>
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -26385,8 +25892,8 @@
       </c>
     </row>
     <row r="7" spans="1:37">
-      <c r="A7" s="51" t="s">
-        <v>14</v>
+      <c r="A7" s="48" t="s">
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -26422,11 +25929,11 @@
         <v>10</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:37">
-      <c r="A8" s="51"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="3">
         <v>0.1</v>
       </c>
@@ -26466,7 +25973,7 @@
       </c>
     </row>
     <row r="9" spans="1:37">
-      <c r="A9" s="51"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="3">
         <v>0.2</v>
       </c>
@@ -26506,7 +26013,7 @@
       </c>
     </row>
     <row r="10" spans="1:37">
-      <c r="A10" s="51"/>
+      <c r="A10" s="48"/>
       <c r="B10" s="3">
         <v>0.3</v>
       </c>
@@ -26546,7 +26053,7 @@
       </c>
     </row>
     <row r="11" spans="1:37">
-      <c r="A11" s="51"/>
+      <c r="A11" s="48"/>
       <c r="B11" s="3">
         <v>0.5</v>
       </c>
@@ -26586,8 +26093,8 @@
       </c>
     </row>
     <row r="13" spans="1:37">
-      <c r="A13" s="51" t="s">
-        <v>15</v>
+      <c r="A13" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>18</v>
@@ -26623,11 +26130,11 @@
         <v>10</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:37">
-      <c r="A14" s="51"/>
+      <c r="A14" s="48"/>
       <c r="B14" s="3">
         <v>0.1</v>
       </c>
@@ -26667,7 +26174,7 @@
       </c>
     </row>
     <row r="15" spans="1:37">
-      <c r="A15" s="51"/>
+      <c r="A15" s="48"/>
       <c r="B15" s="3">
         <v>0.2</v>
       </c>
@@ -26707,7 +26214,7 @@
       </c>
     </row>
     <row r="16" spans="1:37">
-      <c r="A16" s="51"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="3">
         <v>0.3</v>
       </c>
@@ -26747,7 +26254,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="51"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="3">
         <v>0.5</v>
       </c>
@@ -26789,38 +26296,38 @@
     <row r="18" spans="1:13" ht="4.9000000000000004" customHeight="1"/>
     <row r="19" spans="1:13" ht="6" customHeight="1"/>
     <row r="20" spans="1:13">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="47"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="B21" s="49"/>
+      <c r="C21" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="50"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="B21" s="52"/>
-      <c r="C21" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>17</v>
@@ -26956,7 +26463,7 @@
       </c>
       <c r="E26" s="8">
         <f>'Control Onion'!G10</f>
-        <v>4.13</v>
+        <v>4.1300000000000008</v>
       </c>
       <c r="F26" s="8">
         <f>'Control Onion'!H10</f>
@@ -26996,8 +26503,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>12</v>
+      <c r="A1" s="48" t="s">
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -27033,11 +26540,11 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="15" customHeight="1">
-      <c r="A2" s="51"/>
+      <c r="A2" s="48"/>
       <c r="B2" s="3">
         <v>0.1</v>
       </c>
@@ -27075,32 +26582,32 @@
         <f>AVERAGE(C2:L2)</f>
         <v>1.71</v>
       </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="12"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
     </row>
     <row r="3" spans="1:37" ht="15" customHeight="1">
-      <c r="A3" s="51"/>
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.2</v>
       </c>
@@ -27138,32 +26645,32 @@
         <f t="shared" ref="M3:M11" si="0">AVERAGE(C3:L3)</f>
         <v>1.99</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-      <c r="AJ3" s="11"/>
-      <c r="AK3" s="11"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
     </row>
     <row r="4" spans="1:37" ht="15" customHeight="1">
-      <c r="A4" s="51"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
@@ -27203,7 +26710,7 @@
       </c>
     </row>
     <row r="5" spans="1:37" ht="15" customHeight="1">
-      <c r="A5" s="51"/>
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.5</v>
       </c>
@@ -27243,8 +26750,8 @@
       </c>
     </row>
     <row r="7" spans="1:37">
-      <c r="A7" s="51" t="s">
-        <v>14</v>
+      <c r="A7" s="48" t="s">
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -27280,11 +26787,11 @@
         <v>10</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:37">
-      <c r="A8" s="51"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="3">
         <v>0.1</v>
       </c>
@@ -27324,7 +26831,7 @@
       </c>
     </row>
     <row r="9" spans="1:37">
-      <c r="A9" s="51"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="3">
         <v>0.2</v>
       </c>
@@ -27364,7 +26871,7 @@
       </c>
     </row>
     <row r="10" spans="1:37">
-      <c r="A10" s="51"/>
+      <c r="A10" s="48"/>
       <c r="B10" s="3">
         <v>0.3</v>
       </c>
@@ -27404,7 +26911,7 @@
       </c>
     </row>
     <row r="11" spans="1:37">
-      <c r="A11" s="51"/>
+      <c r="A11" s="48"/>
       <c r="B11" s="3">
         <v>0.5</v>
       </c>
@@ -27444,8 +26951,8 @@
       </c>
     </row>
     <row r="13" spans="1:37">
-      <c r="A13" s="51" t="s">
-        <v>15</v>
+      <c r="A13" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>18</v>
@@ -27481,11 +26988,11 @@
         <v>10</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:37">
-      <c r="A14" s="51"/>
+      <c r="A14" s="48"/>
       <c r="B14" s="3">
         <v>0.1</v>
       </c>
@@ -27525,7 +27032,7 @@
       </c>
     </row>
     <row r="15" spans="1:37">
-      <c r="A15" s="51"/>
+      <c r="A15" s="48"/>
       <c r="B15" s="3">
         <v>0.2</v>
       </c>
@@ -27565,7 +27072,7 @@
       </c>
     </row>
     <row r="16" spans="1:37">
-      <c r="A16" s="51"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="3">
         <v>0.3</v>
       </c>
@@ -27605,7 +27112,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="51"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="3">
         <v>0.5</v>
       </c>
@@ -27647,38 +27154,38 @@
     <row r="18" spans="1:13" ht="5.45" customHeight="1"/>
     <row r="19" spans="1:13" ht="5.45" customHeight="1"/>
     <row r="20" spans="1:13">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="47"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="B21" s="49"/>
+      <c r="C21" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="50"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="B21" s="52"/>
-      <c r="C21" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>17</v>
@@ -27814,7 +27321,7 @@
       </c>
       <c r="E26" s="8">
         <f>'Control Onion'!G10</f>
-        <v>4.13</v>
+        <v>4.1300000000000008</v>
       </c>
       <c r="F26" s="8">
         <f>'Control Onion'!H10</f>
@@ -27846,55 +27353,52 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="34" width="9.625" customWidth="1"/>
+    <col min="5" max="33" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="1:17" ht="15" customHeight="1">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="22"/>
-    </row>
-    <row r="2" spans="1:18" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>13</v>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="21"/>
+    </row>
+    <row r="2" spans="1:17" s="11" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="8">
         <v>16.5</v>
@@ -27902,102 +27406,94 @@
       <c r="D2" s="8">
         <v>18.7</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>17.5</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <v>14</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>17.899999999999999</v>
       </c>
-      <c r="H2" s="8">
-        <f>AVERAGE(C2:G2)</f>
-        <v>16.920000000000002</v>
-      </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-    </row>
-    <row r="3" spans="1:18" ht="15" customHeight="1"/>
-    <row r="4" spans="1:18" ht="15" customHeight="1"/>
-    <row r="6" spans="1:18">
-      <c r="D6" s="52" t="s">
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+    </row>
+    <row r="3" spans="1:17" ht="15" customHeight="1"/>
+    <row r="4" spans="1:17" ht="15" customHeight="1"/>
+    <row r="6" spans="1:17">
+      <c r="D6" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="56"/>
+    </row>
+    <row r="7" spans="1:17" ht="28.5" customHeight="1">
+      <c r="D7" s="49"/>
+      <c r="E7" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="59"/>
-    </row>
-    <row r="7" spans="1:18" ht="28.5" customHeight="1">
-      <c r="D7" s="52"/>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="27" customHeight="1">
+    <row r="8" spans="1:17" ht="27" customHeight="1">
       <c r="D8" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="2">
         <f>AVERAGE(C2:G2)</f>
-        <v>16.920000000000002</v>
+        <v>16.919999999999998</v>
       </c>
       <c r="F8" s="2">
         <f>ROUND(_xlfn.STDEV.S(C2:G2),2)</f>
         <v>1.81</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="12"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="12"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="12"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+    <row r="13" spans="1:17">
+      <c r="A13" s="11"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="11"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="11"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -28010,16 +27506,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A2:H16"/>
+  <dimension ref="A2:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="51" t="s">
-        <v>15</v>
+    <row r="2" spans="1:7" ht="16.5">
+      <c r="A2" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -28039,12 +27535,9 @@
       <c r="G2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:7" ht="13.5">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.1</v>
       </c>
@@ -28063,13 +27556,9 @@
       <c r="G3" s="4">
         <v>23.5</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>20.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:7" ht="13.5">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.2</v>
       </c>
@@ -28088,13 +27577,9 @@
       <c r="G4" s="4">
         <v>17.5</v>
       </c>
-      <c r="H4" s="2">
-        <f t="shared" ref="H4:H6" si="0">AVERAGE(C4:G4)</f>
-        <v>19.84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:7" ht="13.5">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.3</v>
       </c>
@@ -28113,13 +27598,9 @@
       <c r="G5" s="4">
         <v>14.5</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="51"/>
+    </row>
+    <row r="6" spans="1:7" ht="13.5">
+      <c r="A6" s="48"/>
       <c r="B6" s="3">
         <v>0.5</v>
       </c>
@@ -28138,28 +27619,23 @@
       <c r="G6" s="4">
         <v>12</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" si="0"/>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="52" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="13.5">
+      <c r="B10" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:7" ht="13.5">
+      <c r="B11" s="49"/>
+      <c r="C11" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="52"/>
-      <c r="C11" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -28167,92 +27643,86 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8">
+    </row>
+    <row r="12" spans="1:7" ht="13.5">
       <c r="B12" s="3">
         <v>0.1</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <f>AVERAGE(C3:G3)</f>
         <v>20.3</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" ref="D12:D15" si="1">ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
+        <f t="shared" ref="D12:D15" si="0">ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>2.17</v>
       </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+    </row>
+    <row r="13" spans="1:7" ht="13.5">
       <c r="B13" s="3">
         <v>0.2</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <f>AVERAGE(C4:G4)</f>
-        <v>19.84</v>
+        <v>19.839999999999996</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.78</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+    </row>
+    <row r="14" spans="1:7" ht="13.5">
       <c r="B14" s="3">
         <v>0.3</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <f>AVERAGE(C5:G5)</f>
         <v>14.9</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.64</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="1:7" ht="13.5">
       <c r="B15" s="3">
         <v>0.5</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <f>AVERAGE(C6:G6)</f>
         <v>12.4</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.86</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+    </row>
+    <row r="16" spans="1:7" ht="13.5">
       <c r="B16" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="23">
         <f>'Control Pea Shoot'!E8</f>
-        <v>16.920000000000002</v>
+        <v>16.919999999999998</v>
       </c>
       <c r="D16" s="2">
         <f>'Control Pea Shoot'!F8</f>
         <v>1.81</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -28270,16 +27740,16 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A2:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A2:G16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="51" t="s">
-        <v>15</v>
+    <row r="2" spans="1:7" ht="16.5">
+      <c r="A2" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -28299,12 +27769,9 @@
       <c r="G2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.1</v>
       </c>
@@ -28323,13 +27790,9 @@
       <c r="G3" s="4">
         <v>19.5</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.2</v>
       </c>
@@ -28348,13 +27811,9 @@
       <c r="G4" s="4">
         <v>20.5</v>
       </c>
-      <c r="H4" s="2">
-        <f t="shared" ref="H4:H6" si="0">AVERAGE(C4:G4)</f>
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.3</v>
       </c>
@@ -28373,13 +27832,9 @@
       <c r="G5" s="4">
         <v>12.5</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>14.28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="51"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="48"/>
       <c r="B6" s="3">
         <v>0.5</v>
       </c>
@@ -28398,28 +27853,23 @@
       <c r="G6" s="4">
         <v>7.5</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" si="0"/>
-        <v>11.44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="61" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="14.45" customHeight="1">
+      <c r="B10" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="58"/>
+      <c r="C11" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="61"/>
-      <c r="C11" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -28427,10 +27877,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="23">
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="22">
         <v>0.1</v>
       </c>
       <c r="C12" s="2">
@@ -28441,13 +27890,12 @@
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>0.82</v>
       </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="23">
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="22">
         <v>0.2</v>
       </c>
       <c r="C13" s="2">
@@ -28458,13 +27906,12 @@
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>0.56999999999999995</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="23">
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="22">
         <v>0.3</v>
       </c>
       <c r="C14" s="2">
@@ -28475,13 +27922,12 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>1.69</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="B15" s="23">
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="22">
         <v>0.5</v>
       </c>
       <c r="C15" s="2">
@@ -28492,33 +27938,30 @@
         <f>ROUND(_xlfn.STDEV.S(C6:G6),2)</f>
         <v>3.67</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" s="24" t="s">
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="2">
         <f>'Control Pea Shoot'!E8</f>
-        <v>16.920000000000002</v>
+        <v>16.919999999999998</v>
       </c>
       <c r="D16" s="2">
         <f>'Control Pea Shoot'!F8</f>
         <v>1.81</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B10:B11"/>
   </mergeCells>
@@ -28529,16 +27972,16 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A2:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
+  <dimension ref="A2:G16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="39" width="9.625" customWidth="1"/>
+    <col min="3" max="38" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="51" t="s">
-        <v>15</v>
+    <row r="2" spans="1:7" ht="16.5">
+      <c r="A2" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -28558,12 +28001,9 @@
       <c r="G2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="51"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="48"/>
       <c r="B3" s="3">
         <v>0.1</v>
       </c>
@@ -28582,13 +28022,9 @@
       <c r="G3" s="4">
         <v>21.2</v>
       </c>
-      <c r="H3" s="2">
-        <f>AVERAGE(C3:G3)</f>
-        <v>21.32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="51"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="48"/>
       <c r="B4" s="3">
         <v>0.2</v>
       </c>
@@ -28607,13 +28043,9 @@
       <c r="G4" s="4">
         <v>17.7</v>
       </c>
-      <c r="H4" s="2">
-        <f t="shared" ref="H4:H6" si="0">AVERAGE(C4:G4)</f>
-        <v>18.82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="51"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="48"/>
       <c r="B5" s="3">
         <v>0.3</v>
       </c>
@@ -28632,13 +28064,9 @@
       <c r="G5" s="4">
         <v>11</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>12.96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="51"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="48"/>
       <c r="B6" s="3">
         <v>0.5</v>
       </c>
@@ -28657,28 +28085,23 @@
       <c r="G6" s="4">
         <v>6</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" si="0"/>
-        <v>7.54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="61" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="14.45" customHeight="1">
+      <c r="B10" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="58"/>
+      <c r="C11" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="61"/>
-      <c r="C11" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -28686,10 +28109,9 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="23">
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="22">
         <v>0.1</v>
       </c>
       <c r="C12" s="2">
@@ -28700,13 +28122,12 @@
         <f>ROUND(_xlfn.STDEV.S(C3:G3),2)</f>
         <v>0.51</v>
       </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="23">
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="22">
         <v>0.2</v>
       </c>
       <c r="C13" s="2">
@@ -28717,13 +28138,12 @@
         <f>ROUND(_xlfn.STDEV.S(C4:G4),2)</f>
         <v>1.9</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="23">
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="22">
         <v>0.3</v>
       </c>
       <c r="C14" s="2">
@@ -28734,13 +28154,12 @@
         <f>ROUND(_xlfn.STDEV.S(C5:G5),2)</f>
         <v>1.92</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="B15" s="23">
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="22">
         <v>0.5</v>
       </c>
       <c r="C15" s="2">
@@ -28751,33 +28170,30 @@
         <f>ROUND(_xlfn.STDEV.S(C6:G6),2)</f>
         <v>2.83</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" s="24" t="s">
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="2">
         <f>'Control Pea Shoot'!E8</f>
-        <v>16.920000000000002</v>
+        <v>16.919999999999998</v>
       </c>
       <c r="D16" s="2">
         <f>'Control Pea Shoot'!F8</f>
         <v>1.81</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B10:B11"/>
   </mergeCells>
